--- a/batchstudent/1/AnhDThe187386/Results/AnhDThe187386/TC5/GradeDetail.xlsx
+++ b/batchstudent/1/AnhDThe187386/Results/AnhDThe187386/TC5/GradeDetail.xlsx
@@ -1059,7 +1059,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1118,7 +1118,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>47</x:v>
@@ -1171,7 +1171,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1227,7 +1227,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1286,7 +1286,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
         <x:v>47</x:v>
@@ -1342,7 +1342,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="R7" s="2" t="s">
         <x:v>47</x:v>
@@ -1395,7 +1395,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
@@ -1454,7 +1454,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>63</x:v>
@@ -1507,7 +1507,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
@@ -1566,7 +1566,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
         <x:v>63</x:v>
@@ -1619,7 +1619,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P12" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="Q12" s="0">
         <x:v>4000</x:v>
@@ -1678,7 +1678,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q13" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="R13" s="3" t="s">
         <x:v>63</x:v>
@@ -1731,7 +1731,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P14" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="Q14" s="0">
         <x:v>4000</x:v>
@@ -1787,7 +1787,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
@@ -1846,7 +1846,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q16" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="R16" s="3" t="s">
         <x:v>63</x:v>
@@ -1902,7 +1902,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q17" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="R17" s="3" t="s">
         <x:v>63</x:v>
@@ -1955,7 +1955,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P18" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="Q18" s="0">
         <x:v>4000</x:v>
@@ -2014,7 +2014,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q19" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
         <x:v>63</x:v>
@@ -2067,7 +2067,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P20" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="Q20" s="0">
         <x:v>4000</x:v>
@@ -2126,7 +2126,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="R21" s="3" t="s">
         <x:v>63</x:v>
@@ -2179,7 +2179,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="Q22" s="0">
         <x:v>4000</x:v>
@@ -2238,7 +2238,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q23" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="R23" s="3" t="s">
         <x:v>63</x:v>
@@ -2291,7 +2291,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P24" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="Q24" s="0">
         <x:v>4000</x:v>
@@ -2347,7 +2347,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="P25" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="Q25" s="0">
         <x:v>4000</x:v>
@@ -2406,7 +2406,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q26" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="R26" s="3" t="s">
         <x:v>63</x:v>
@@ -2462,7 +2462,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q27" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="R27" s="3" t="s">
         <x:v>63</x:v>
@@ -2515,7 +2515,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P28" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="Q28" s="0">
         <x:v>4000</x:v>
@@ -2574,7 +2574,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q29" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="R29" s="3" t="s">
         <x:v>63</x:v>
@@ -2627,7 +2627,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P30" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="Q30" s="0">
         <x:v>4000</x:v>
@@ -2686,7 +2686,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q31" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="R31" s="3" t="s">
         <x:v>63</x:v>
@@ -2739,7 +2739,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P32" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="Q32" s="0">
         <x:v>4000</x:v>
@@ -2798,7 +2798,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q33" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="R33" s="3" t="s">
         <x:v>63</x:v>
@@ -2851,7 +2851,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P34" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="Q34" s="0">
         <x:v>4000</x:v>
@@ -2907,7 +2907,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="P35" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="Q35" s="0">
         <x:v>4000</x:v>
@@ -2966,7 +2966,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q36" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="R36" s="3" t="s">
         <x:v>63</x:v>
@@ -3022,7 +3022,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q37" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="R37" s="3" t="s">
         <x:v>63</x:v>
@@ -3075,7 +3075,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P38" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="Q38" s="0">
         <x:v>4000</x:v>
@@ -3134,7 +3134,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q39" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="R39" s="3" t="s">
         <x:v>63</x:v>
@@ -3187,7 +3187,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P40" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="Q40" s="0">
         <x:v>4000</x:v>
@@ -3246,7 +3246,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q41" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="R41" s="3" t="s">
         <x:v>63</x:v>
@@ -3299,7 +3299,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P42" s="0">
-        <x:v>53926</x:v>
+        <x:v>41626</x:v>
       </x:c>
       <x:c r="Q42" s="0">
         <x:v>4000</x:v>
@@ -3358,7 +3358,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q43" s="0">
-        <x:v>53926</x:v>
+        <x:v>41626</x:v>
       </x:c>
       <x:c r="R43" s="3" t="s">
         <x:v>63</x:v>
@@ -3411,7 +3411,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P44" s="0">
-        <x:v>53926</x:v>
+        <x:v>41626</x:v>
       </x:c>
       <x:c r="Q44" s="0">
         <x:v>4000</x:v>
@@ -3467,7 +3467,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="P45" s="0">
-        <x:v>53926</x:v>
+        <x:v>41626</x:v>
       </x:c>
       <x:c r="Q45" s="0">
         <x:v>4000</x:v>
@@ -3526,7 +3526,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q46" s="0">
-        <x:v>53926</x:v>
+        <x:v>41626</x:v>
       </x:c>
       <x:c r="R46" s="3" t="s">
         <x:v>63</x:v>
@@ -3582,7 +3582,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q47" s="0">
-        <x:v>53926</x:v>
+        <x:v>41626</x:v>
       </x:c>
       <x:c r="R47" s="3" t="s">
         <x:v>63</x:v>
@@ -3635,7 +3635,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P48" s="0">
-        <x:v>53926</x:v>
+        <x:v>41626</x:v>
       </x:c>
       <x:c r="Q48" s="0">
         <x:v>4000</x:v>
@@ -3694,7 +3694,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q49" s="0">
-        <x:v>53926</x:v>
+        <x:v>41626</x:v>
       </x:c>
       <x:c r="R49" s="3" t="s">
         <x:v>63</x:v>
@@ -3747,7 +3747,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P50" s="0">
-        <x:v>53926</x:v>
+        <x:v>41626</x:v>
       </x:c>
       <x:c r="Q50" s="0">
         <x:v>4000</x:v>
@@ -3806,7 +3806,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q51" s="0">
-        <x:v>53926</x:v>
+        <x:v>41626</x:v>
       </x:c>
       <x:c r="R51" s="3" t="s">
         <x:v>63</x:v>
